--- a/data/trans_camb/P32A-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P32A-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 3,97</t>
+          <t>-0,25; 3,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,31; 5,13</t>
+          <t>0,76; 5,26</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,8; 6,02</t>
+          <t>0,95; 5,9</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 0,0</t>
+          <t>-2,78; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 5,34</t>
+          <t>-0,56; 5,24</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 3,31</t>
+          <t>-1,0; 3,59</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 2,49</t>
+          <t>-0,28; 2,58</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,57; 4,54</t>
+          <t>0,57; 4,5</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,68; 4,76</t>
+          <t>0,83; 5,06</t>
         </is>
       </c>
     </row>
@@ -783,17 +783,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-20,85; 587,54</t>
+          <t>-22,47; 562,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 819,9</t>
+          <t>17,42; 791,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13,26; 903,61</t>
+          <t>16,07; 851,27</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-42,66; 409,19</t>
+          <t>-28,29; 441,42</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,9; 689,39</t>
+          <t>10,54; 720,08</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>18,42; 711,63</t>
+          <t>28,82; 788,5</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,94</t>
+          <t>0,65; 3,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 1,74</t>
+          <t>-0,24; 1,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 0,95</t>
+          <t>-0,86; 0,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,64</t>
+          <t>0,28; 2,78</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 1,42</t>
+          <t>-0,18; 1,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 2,5</t>
+          <t>-0,03; 2,47</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,47</t>
+          <t>0,75; 2,54</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,02; 1,31</t>
+          <t>-0,03; 1,4</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 1,18</t>
+          <t>-0,31; 1,21</t>
         </is>
       </c>
     </row>
@@ -999,17 +999,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>26,66; 400,82</t>
+          <t>25,34; 455,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-18,5; 267,4</t>
+          <t>-18,37; 281,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-56,84; 171,37</t>
+          <t>-62,71; 142,81</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1029,17 +1029,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>54,19; 476,93</t>
+          <t>63,0; 527,98</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 262,3</t>
+          <t>-8,62; 270,12</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-33,67; 205,39</t>
+          <t>-31,61; 241,53</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 1,22</t>
+          <t>-0,92; 1,19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 1,09</t>
+          <t>-1,0; 1,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 2,93</t>
+          <t>0,05; 2,86</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 0,81</t>
+          <t>-2,1; 0,81</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,3; 5,18</t>
+          <t>0,31; 4,88</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 2,46</t>
+          <t>-0,73; 2,46</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 0,78</t>
+          <t>-0,84; 0,79</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,03; 2,4</t>
+          <t>-0,06; 2,26</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,18; 2,17</t>
+          <t>0,1; 2,33</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-58,93; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1250,12 +1250,12 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-29,04; 1458,65</t>
+          <t>-52,68; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-7,18; 1248,92</t>
+          <t>-15,63; 1434,24</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,7; 2,41</t>
+          <t>0,67; 2,34</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,79</t>
+          <t>0,24; 1,73</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 1,52</t>
+          <t>-0,02; 1,58</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 1,32</t>
+          <t>-0,12; 1,34</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,92</t>
+          <t>0,32; 1,95</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,15; 2,04</t>
+          <t>0,16; 2,18</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,57; 1,78</t>
+          <t>0,55; 1,88</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,54</t>
+          <t>0,34; 1,5</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,44</t>
+          <t>0,21; 1,47</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>40,42; 311,9</t>
+          <t>44,07; 314,0</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>11,76; 233,69</t>
+          <t>10,91; 218,0</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-7,52; 208,44</t>
+          <t>-3,67; 221,33</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-55,61; 1060,29</t>
+          <t>-61,07; 1054,78</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>13,39; 1568,78</t>
+          <t>13,75; 1621,48</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,26; 1568,59</t>
+          <t>-4,69; 1744,02</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>53,12; 292,2</t>
+          <t>48,05; 311,7</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>28,26; 252,47</t>
+          <t>31,0; 248,34</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>12,36; 235,61</t>
+          <t>13,14; 229,24</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P32A-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P32A-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3,19</t>
+          <t>2,88</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,72</t>
+          <t>0,63</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2,69</t>
+          <t>2,41</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 3,91</t>
+          <t>-0,28; 3,93</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,76; 5,26</t>
+          <t>0,47; 5,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,95; 5,9</t>
+          <t>0,85; 6,03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 0,0</t>
+          <t>-3,17; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 5,24</t>
+          <t>-0,54; 5,2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 3,59</t>
+          <t>-1,08; 3,2</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 2,58</t>
+          <t>-0,46; 2,66</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,57; 4,5</t>
+          <t>0,46; 4,36</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,83; 5,06</t>
+          <t>0,58; 4,53</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>224,97%</t>
+          <t>202,94%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>130,05%</t>
+          <t>114,93%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>226,23%</t>
+          <t>201,95%</t>
         </is>
       </c>
     </row>
@@ -783,17 +783,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-22,47; 562,45</t>
+          <t>-27,77; 684,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17,42; 791,56</t>
+          <t>-0,32; 824,03</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16,07; 851,27</t>
+          <t>22,13; 976,02</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-28,29; 441,42</t>
+          <t>-35,83; 379,63</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,54; 720,08</t>
+          <t>12,4; 643,69</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>28,82; 788,5</t>
+          <t>-0,64; 676,55</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-0,01</t>
+          <t>0,03</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,19</t>
+          <t>2,35</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,41</t>
+          <t>0,82</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,65; 3,15</t>
+          <t>0,55; 2,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 1,83</t>
+          <t>-0,24; 1,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 0,87</t>
+          <t>-0,86; 0,91</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,78</t>
+          <t>0,33; 2,61</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 1,42</t>
+          <t>-0,1; 1,36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 2,47</t>
+          <t>1,06; 4,41</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,54</t>
+          <t>0,65; 2,49</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 1,4</t>
+          <t>-0,06; 1,33</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 1,21</t>
+          <t>0,03; 1,69</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-0,97%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>620,96%</t>
+          <t>1229,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>52,45%</t>
+          <t>104,04%</t>
         </is>
       </c>
     </row>
@@ -999,17 +999,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>25,34; 455,55</t>
+          <t>26,99; 437,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-18,37; 281,94</t>
+          <t>-18,74; 273,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-62,71; 142,81</t>
+          <t>-57,46; 127,2</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1029,17 +1029,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>63,0; 527,98</t>
+          <t>47,74; 513,74</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-8,62; 270,12</t>
+          <t>-7,65; 276,55</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-31,61; 241,53</t>
+          <t>-1,94; 308,57</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,27</t>
+          <t>1,58</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,94</t>
+          <t>1,13</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1,13</t>
+          <t>1,39</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 1,19</t>
+          <t>-0,85; 1,41</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 1,1</t>
+          <t>-1,05; 1,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,05; 2,86</t>
+          <t>0,1; 3,24</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 0,81</t>
+          <t>-2,09; 0,81</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,31; 4,88</t>
+          <t>0,34; 4,93</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 2,46</t>
+          <t>-0,53; 2,93</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 0,79</t>
+          <t>-0,81; 0,84</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 2,26</t>
+          <t>0,05; 2,3</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,1; 2,33</t>
+          <t>0,33; 2,68</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>242,42%</t>
+          <t>301,06%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>177,88%</t>
+          <t>214,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>215,78%</t>
+          <t>264,71%</t>
         </is>
       </c>
     </row>
@@ -1225,37 +1225,37 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
+          <t>-26,25; —</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-52,68; —</t>
+          <t>-27,15; 1330,85</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-15,63; 1434,24</t>
+          <t>-19,08; 1393,09</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,72</t>
+          <t>0,76</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,06</t>
+          <t>1,83</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,8</t>
+          <t>1,11</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,67; 2,34</t>
+          <t>0,63; 2,49</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,24; 1,73</t>
+          <t>0,21; 1,74</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 1,58</t>
+          <t>0,03; 1,51</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 1,34</t>
+          <t>-0,12; 1,33</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,95</t>
+          <t>0,31; 1,88</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,16; 2,18</t>
+          <t>0,9; 3,06</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,55; 1,88</t>
+          <t>0,55; 1,82</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,34; 1,5</t>
+          <t>0,35; 1,49</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,47</t>
+          <t>0,51; 1,78</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>67,2%</t>
+          <t>71,15%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>319,88%</t>
+          <t>553,64%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>134,21%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>44,07; 314,0</t>
+          <t>40,63; 322,17</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>10,91; 218,0</t>
+          <t>11,03; 222,7</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 221,33</t>
+          <t>-1,87; 204,17</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-61,07; 1054,78</t>
+          <t>-45,93; 1299,42</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>13,75; 1621,48</t>
+          <t>12,87; 1513,41</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 1744,02</t>
+          <t>100,47; 2690,52</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>48,05; 311,7</t>
+          <t>45,55; 286,64</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>31,0; 248,34</t>
+          <t>26,44; 241,23</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>13,14; 229,24</t>
+          <t>40,35; 285,34</t>
         </is>
       </c>
     </row>
